--- a/docs/import-template.xlsx
+++ b/docs/import-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="54">
   <si>
     <t>SPU编号</t>
   </si>
@@ -31,6 +31,9 @@
     <t>金属底色</t>
   </si>
   <si>
+    <t>主石尺寸(mm)</t>
+  </si>
+  <si>
     <t>尺码</t>
   </si>
   <si>
@@ -85,6 +88,9 @@
     <t>银色,金色,玫瑰金</t>
   </si>
   <si>
+    <t>8,10</t>
+  </si>
+  <si>
     <t>6,7,8,9</t>
   </si>
   <si>
@@ -116,6 +122,9 @@
   </si>
   <si>
     <t>银色,金色</t>
+  </si>
+  <si>
+    <t>6,8</t>
   </si>
   <si>
     <t>40,45,50</t>
@@ -585,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -593,15 +602,16 @@
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="8" width="14" customWidth="1"/>
-    <col min="9" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="35" customWidth="1"/>
-    <col min="12" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="30" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
+    <col min="10" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="35" customWidth="1"/>
+    <col min="13" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="25" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -656,178 +666,190 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -846,8 +868,9 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -866,8 +889,9 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -886,8 +910,9 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -906,8 +931,9 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -926,8 +952,9 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -946,8 +973,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -966,8 +994,9 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -986,8 +1015,9 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1006,8 +1036,9 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1026,8 +1057,9 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1046,8 +1078,9 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1066,8 +1099,9 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1086,8 +1120,9 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1106,8 +1141,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1126,8 +1162,9 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1146,8 +1183,9 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1166,8 +1204,9 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1186,8 +1225,9 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1206,8 +1246,9 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1226,8 +1267,9 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1246,8 +1288,9 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1266,8 +1309,9 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1286,8 +1330,9 @@
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1306,8 +1351,9 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1326,8 +1372,9 @@
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1346,8 +1393,9 @@
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1366,8 +1414,9 @@
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1386,8 +1435,9 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1406,8 +1456,9 @@
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1426,8 +1477,9 @@
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1446,8 +1498,9 @@
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S36" s="3"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1466,8 +1519,9 @@
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
-    </row>
-    <row r="38" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S37" s="3"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1486,8 +1540,9 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
-    </row>
-    <row r="39" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S38" s="3"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1506,8 +1561,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1526,8 +1582,9 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1546,10 +1603,53 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:R41"/>
+    <mergeCell ref="A6:S43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
